--- a/output/global/cross-workspace-inventory.xlsx
+++ b/output/global/cross-workspace-inventory.xlsx
@@ -15,9 +15,11 @@
     <sheet name="DuplicateFlows" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workspaces'!$A$3:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AllForms'!$A$3:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AllWorkflows'!$A$3:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workspaces'!$A$3:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AllForms'!$A$3:$E$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AllWorkflows'!$A$3:$H$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FormNameCollisions'!$A$3:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DuplicateFlows'!$A$3:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -584,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -669,29 +671,53 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>SCE - Building Electrification</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1578</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
           <t>socal-whp</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SCE - ESA Whole Home (PP/D)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C6" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D6" s="9" t="n">
         <v>2296</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F6" s="9" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F5"/>
+  <autoFilter ref="A3:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -702,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -776,12 +802,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>socal-whp</t>
+          <t>sce-be</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>300 - Account Management</t>
+          <t>200 - Account</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -790,173 +816,173 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>353</v>
+        <v>235</v>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>so_cal-esa_whole_home_pp_d__300-account_management_v342_design.json</t>
+          <t>sce-building_electrification.json</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>socal-whp</t>
+          <t>sce-be</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>310 - Enrollment Intake</t>
+          <t>ContactAttemptsGrid</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Spoke</t>
+          <t>Subform</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>161</v>
+        <v>3</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>so_cal-esa_whole_home_pp_d__310-enrollment_intake_v97_design.json</t>
+          <t>sce-building_electrification.json</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>socal-whp</t>
+          <t>sce-be</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>315 - SoCal WHP Assessment</t>
+          <t>NotesTable</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Spoke</t>
+          <t>Subform</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>585</v>
+        <v>4</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>so_cal-esa_whole_home_pp_d__315-so_cal_whp_assessment_v105_design.json</t>
+          <t>sce-building_electrification.json</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>socal-whp</t>
+          <t>sce-be</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>325 - SoCal Installation</t>
+          <t>HouseholdMemberInformation</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Spoke</t>
+          <t>Subform</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>814</v>
+        <v>6</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>so_cal-esa_whole_home_pp_d__325-so_cal_installation_v92_design.json</t>
+          <t>sce-building_electrification.json</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>socal-whp</t>
+          <t>sce-be</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>395 - Inspection Work Order</t>
+          <t>CampaignDetails</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Spoke</t>
+          <t>Subform</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>134</v>
+        <v>6</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>so_cal-esa_whole_home_pp_d__395-inspection_work_order_v77_design__1_.json</t>
+          <t>sce-building_electrification.json</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>socal-whp</t>
+          <t>sce-be</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>399 - Measures</t>
+          <t>Climate Zones</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Spoke</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>so_cal-esa_whole_home_pp_d__399-measures_v28_design.json</t>
+          <t>sce-building_electrification.json</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>socal-whp</t>
+          <t>sce-be</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Fee Schedule</t>
+          <t>210 - Enrollment &amp; Assessment Form</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Spoke</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>so_cal-esa_whole_home_pp_d__fee_schedule_v9_design.json</t>
+          <t>sce-building_electrification.json</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>socal-whp</t>
+          <t>sce-be</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>255 - BE Installation Form</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -965,41 +991,941 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>172</v>
+        <v>651</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>so_cal-esa_whole_home_pp_d__invoice_v169_design__1_.json</t>
+          <t>sce-building_electrification.json</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>HouseholdMemberInformation (210 - Enrollment &amp; Assessment Form)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>RoomACGrid</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>CorrectionNotesGrid</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>ScopeOfWorkGrid</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>InsulationGrid</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>InstalledInsulation</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>PermitInformation</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>ExistingRoomAC</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>ExistingEVAPCoolerGrid</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>ExistingThermostat</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>NewThermostatInformation</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>ExistingMiniSplitSystem</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NewMiniSplitSystem</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>NewSystemHeadUnitInformation</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>AlarmDetailGrid</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>CorrectioNotes</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>MinorHomeRepairGrid</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>AdditionalPhotosGrid</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Census Tract</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Fee Schedule</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>InvoiceDetails</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>FinalInvoiceMeasures</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>DownPaymentReviewGrid</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>InvoiceNoteGrid</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>AmendmentsGrid</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>AdjustmentGrid</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Subform</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>sce-building_electrification.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
           <t>socal-whp</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>300 - Account Management</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Hub</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>353</v>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>so_cal-esa_whole_home_pp_d__300-account_management_v342_design.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>socal-whp</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>310 - Enrollment Intake</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>161</v>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>so_cal-esa_whole_home_pp_d__310-enrollment_intake_v97_design.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>socal-whp</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>315 - SoCal WHP Assessment</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>585</v>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>so_cal-esa_whole_home_pp_d__315-so_cal_whp_assessment_v105_design.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>socal-whp</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>325 - SoCal Installation</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>814</v>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>so_cal-esa_whole_home_pp_d__325-so_cal_installation_v92_design.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>socal-whp</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>395 - Inspection Work Order</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>134</v>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>so_cal-esa_whole_home_pp_d__395-inspection_work_order_v77_design__1_.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>socal-whp</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>399 - Measures</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>so_cal-esa_whole_home_pp_d__399-measures_v28_design.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>socal-whp</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Fee Schedule</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>so_cal-esa_whole_home_pp_d__fee_schedule_v9_design.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>socal-whp</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>so_cal-esa_whole_home_pp_d__invoice_v169_design__1_.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>socal-whp</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Climate Zones</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Lookup</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>(no JSON)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E13"/>
+  <autoFilter ref="A3:E49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1010,16 +1936,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1047,20 +1974,25 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
           <t>TriggerForm</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>TriggerAction</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>TargetForms</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Writes</t>
         </is>
@@ -1084,20 +2016,25 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
+          <t>Active/Disabled</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
           <t>Form that fires it</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Create/Update/Delete</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Forms it writes</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Field writes</t>
         </is>
@@ -1106,40 +2043,829 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_INT</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Customer Interest Receipt</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>200 - Account</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>APPROVAL_NOT</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Approval Notice Issue</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>200 - Account</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>DESKTOP_REVI</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Desktop Review</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>210 - Enrollment &amp; Assessment Form</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ENROLLMENT_A</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Enrollment Approved</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>210 - Enrollment &amp; Assessment Form</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>REQUIRES_COR</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Requires Corrections</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>210 - Enrollment &amp; Assessment Form</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>PENDING_REVI</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Pending Reviews</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>210 - Enrollment &amp; Assessment Form</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>RESUBMISSION</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Resubmission for Corrections</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>210 - Enrollment &amp; Assessment Form</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr"/>
+      <c r="H11" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW_NOTIF</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Review Notification (Operations)</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>210 - Enrollment &amp; Assessment Form</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>INSTALLATION</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Installation Desktop Review</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>255 - BE Installation Form</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr"/>
+      <c r="H13" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>INSTALLATION_2</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Installation Approved</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>255 - BE Installation Form</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr"/>
+      <c r="H14" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>INSTALLATION_3</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Installation Requires Corrections</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>255 - BE Installation Form</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>PENDING_REVI_2</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Pending Reviews</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>255 - BE Installation Form</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW_NOTIF_2</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Review Notification (Operations)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>255 - BE Installation Form</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>INVOICE_SUBM</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Invoice Submitted by Contractor - Final</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>INVOICE_SUBM_2</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Invoice Submitted by Contractor - Down Payment</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Approved by Coordinator - Down Payment</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED_BY__2</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Approved by PM - Down Payment</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED_BY__3</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Approved by PM - Final Invoice</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>CORRECTIONS_</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Corrections Required - Down Payment</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>INVOICE_REJE</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Invoice Rejected by Management - Final</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>CORRECTIONS__2</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Corrections Required - Final</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW_NOTIF_3</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Review Notification (Operations)</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr"/>
+      <c r="H26" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
           <t>socal-whp</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>INSPECT-01</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Create Inspection</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>300 - Account Management</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>395 - Inspection Work Order</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="H27" s="9" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G5"/>
+  <autoFilter ref="A3:H27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1150,7 +2876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1210,7 +2936,68 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Climate Zones</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>sce-be, socal-whp</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Fee Schedule</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>sce-be, socal-whp</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>sce-be, socal-whp</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1221,7 +3008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -1281,7 +3068,68 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Update -&gt; (no target)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>sce-be/APPROVAL_NOT, sce-be/DESKTOP_REVI, sce-be/ENROLLMENT_A, sce-be/REQUIRES_COR, sce-be/RESUBMISSION, sce-be/REVIEW_NOTIF, sce-be/INSTALLATION, sce-be/INSTALLATION_2, sce-be/INSTALLATION_3, sce-be/REVIEW_NOTIF_2, sce-be/INVOICE_SUBM, sce-be/APPROVED_BY_, sce-be/APPROVED_BY__2, sce-be/APPROVED_BY__3, sce-be/CORRECTIONS_, sce-be/INVOICE_REJE, sce-be/CORRECTIONS__2, sce-be/REVIEW_NOTIF_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>(none) -&gt; (no target)</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>sce-be/PENDING_REVI, sce-be/PENDING_REVI_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Create -&gt; (no target)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>sce-be/CUSTOMER_INT, sce-be/INVOICE_SUBM_2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/global/cross-workspace-inventory.xlsx
+++ b/output/global/cross-workspace-inventory.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workspaces" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AllForms" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AllWorkflows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormNameCollisions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DuplicateFlows" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkflowReuse" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormFamilies" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldTemplates" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Workspaces" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AllForms" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AllWorkflows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FormNameCollisions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DuplicateFlows" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="WorkflowReuse" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="FormFamilies" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FieldTemplates" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workspaces'!$A$3:$F$9</definedName>

--- a/output/global/cross-workspace-inventory.xlsx
+++ b/output/global/cross-workspace-inventory.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AllForms'!$A$3:$F$318</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AllWorkflows'!$A$3:$J$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FormNameCollisions'!$A$3:$D$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DuplicateFlows'!$A$3:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DuplicateFlows'!$A$3:$D$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'WorkflowReuse'!$A$3:$I$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FormFamilies'!$A$3:$F$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'FieldTemplates'!$A$3:$D$2755</definedName>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Enrollment Intake - Form 01 record is updated, and only if Submission Status is 'Ready for Review' and Review Status is at least 'Enrollment Approved'.</t>
+          <t>Runs when a Enrollment Intake - Form 01 record is updated, and only if Submission Status is 'Ready for Review' and Review Status compares to 'Enrollment Approved'.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Assessment Intake - Form 02 record is updated, and only if EE Submission Status compares to 'None'.</t>
+          <t>Runs when a Assessment Intake - Form 02 record is updated, and only if EE Submission Status compares to 'one of: EE Ready for Review, Previously Approved'.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Account Management (00) record is updated, and only if Work Order Measure Qty is not '2025-05-20T14:02:00-07:00' and Project Stage compares to 'None'.</t>
+          <t>Runs when a Account Management (00) record is updated, and only if Work Order Measure Qty is not '2025-05-20T14:02:00-07:00' and Project Stage compares to 'one of: Lead, Enrollment, Completed, Data Transfer, Historical, SAEL, Inspection'.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Installation - Form 03 record is updated, and only if Submission Status is 'Ready for Review' and Review Status is at least 'Enrollment Approved'.</t>
+          <t>Runs when a Installation - Form 03 record is updated, and only if Submission Status is 'Ready for Review' and Review Status compares to 'Enrollment Approved'.</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Solar Photovoltaic record is updated, and only if Review Status is at least 'Enrollment Approved' and Submission Status is 'Ready for Review'.</t>
+          <t>Runs when a Solar Photovoltaic record is updated, and only if Review Status compares to 'Enrollment Approved' and Submission Status is 'Ready for Review'.</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Inspections record is updated, and only if Note Reply compares to 'None'.</t>
+          <t>Runs when a Inspections record is updated, and only if NoteReply ?.</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Inspections record is updated, and only if Inspection Status compares to 'None'.</t>
+          <t>Runs when a Inspections record is updated, and only if ComputedInspectionStatus ?.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Enrollment Intake - Form 01 record is updated, and only if Enrollment Status compares to 'None' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a Enrollment Intake - Form 01 record is updated, and only if ComputedStatus ? and ReviewerName_c ?.</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Assessment Intake - Form 02 record is updated, and only if Submission Status compares to 'None' and EE Review Name compares to 'None'.</t>
+          <t>Runs when a Assessment Intake - Form 02 record is updated, and only if OverallSubmissionStatus ? and EEReviewName_c ?.</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Assessment Intake - Form 02 record is updated, and only if Submission Status compares to 'None' and SPV Review Name compares to 'None'.</t>
+          <t>Runs when a Assessment Intake - Form 02 record is updated, and only if OverallSubmissionStatus ? and SPVReviewName_c ?.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Installation - Form 03 record is updated, and only if Installation Status compares to 'None' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a Installation - Form 03 record is updated, and only if InstallationStatus_c ? and ReviewerName_c ?.</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Processor Name (Final) compares to 'None'.</t>
+          <t>Runs when a Invoice record is updated, and only if ProcessorName_Final_c ?.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Runs when a new Invoice record is created, and only if Contractor is at least '06b924d0-99ae-a554-1893-3a12bf2fd6a8' and Contractor compares to 'None'.</t>
+          <t>Runs when a new Invoice record is created, and only if Contractor compares to '06b924d0-99ae-a554-1893-3a12bf2fd6a8' and Contractor ?.</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Invoice Number (Final) compares to 'None'.</t>
+          <t>Runs when a Invoice record is updated, and only if InvoiceNumber_Final ?.</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Invoice Status (DP) is 'Rejected' and Invoice Number (Final) compares to 'None' and Assigned User (Final) is 'Jose Landeros'.</t>
+          <t>Runs when a Invoice record is updated, and only if Invoice Status (DP) is 'Rejected' and InvoiceNumber_Final ? and Assigned User (Final) is 'Jose Landeros'.</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 210 - Enrollment &amp; Assessment Form record is updated, and only if MAROMA Review Status compares to 'Pending Review' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 210 - Enrollment &amp; Assessment Form record is updated, and only if MAROMA Review Status compares to 'Pending Review' and ApprovedByText ?.</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 255 - BE Installation Form record is updated, and only if Installation Status compares to 'Draft' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 255 - BE Installation Form record is updated, and only if Installation Status compares to 'Draft' and ReviewerName_C ?.</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Invoice Status (Final) compares to 'None' and Processor Name compares to 'None'.</t>
+          <t>Runs when a Invoice record is updated, and only if InvoiceStatusSummary ? and ProcessorName_c ?.</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -11340,7 +11340,11 @@
           <t>Create</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr"/>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>210 - Enrollment &amp; Assessment Form</t>
+        </is>
+      </c>
       <c r="J49" s="9" t="n">
         <v>0</v>
       </c>
@@ -11363,7 +11367,7 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Runs when a new 255 - BE Installation Form record is created, and only if Enrollment Number compares to 'None'.</t>
+          <t>Runs when a new 255 - BE Installation Form record is created, and only if EnrollmentNumber ?.</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -11386,7 +11390,11 @@
           <t>Create</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr"/>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>255 - BE Installation Form</t>
+        </is>
+      </c>
       <c r="J50" s="9" t="n">
         <v>0</v>
       </c>
@@ -11739,7 +11747,7 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 415 - San Diego WHP Assessment record is updated, and only if Review Status compares to 'Assessment Approved'.</t>
+          <t>Runs when a 415 - San Diego WHP Assessment record is updated, and only if Review Status compares to 'one of: Assessment Approved, Bid Approved, Bid Approved—Verify Savings'.</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -12157,7 +12165,7 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Account Management (400) record is updated, and only if Final Invoice Amount compares to 'None' or Final Invoice Number compares to 'None'.</t>
+          <t>Runs when a Account Management (400) record is updated, and only if FinalInvoiceAmount ? or FinalInvoiceNumber ?.</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -12249,7 +12257,7 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 410 - WH Enrollment record is updated, and only if Submission Status is 'None' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 410 - WH Enrollment record is updated, and only if OverallSubmissionStatus == and ReviewerName_c ?.</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -12295,7 +12303,7 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 415 - San Diego WHP Assessment record is updated, and only if Assessment Status compares to 'Draft' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 415 - San Diego WHP Assessment record is updated, and only if Assessment Status compares to 'Draft' and ReviewerName_c ?.</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -12341,7 +12349,7 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 425 - San Diego Installation record is updated, and only if Installation Status compares to 'None' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 425 - San Diego Installation record is updated, and only if ComputedStatus ? and ReviewerName_c ?.</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -12387,7 +12395,7 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Invoice Status compares to 'None' and Processor Name compares to 'None'.</t>
+          <t>Runs when a Invoice record is updated, and only if InvoiceStatusSummary ? and ProcessorName_c ?.</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -12479,7 +12487,7 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 410 - WH Enrollment record is updated, and only if Submission Status compares to 'None'.</t>
+          <t>Runs when a 410 - WH Enrollment record is updated, and only if OverallSubmissionStatus ?.</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -12529,7 +12537,7 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 415 - San Diego WHP Assessment record is updated, and only if Review Status compares to 'None'.</t>
+          <t>Runs when a 415 - San Diego WHP Assessment record is updated, and only if Review Status compares to 'one of: Assessment Approved, Retrofit in Progress, Pending Review'.</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -12602,7 +12610,11 @@
           <t>Create</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr"/>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>Account Management (400)</t>
+        </is>
+      </c>
       <c r="J76" s="9" t="n">
         <v>0</v>
       </c>
@@ -12855,7 +12867,7 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 315 - SoCal WHP Assessment record is updated, and only if Assessment Status compares to 'Corrections Required' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 315 - SoCal WHP Assessment record is updated, and only if Assessment Status compares to 'Corrections Required' and ReviewerName_c ?.</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -13039,7 +13051,7 @@
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 395 - Inspection Work Order record is updated, and only if Inspection Status compares to 'None' and Post-Inspection Status is at least 'Open'.</t>
+          <t>Runs when a 395 - Inspection Work Order record is updated, and only if ComputedInspectionStatus ? and Post-Inspection Status compares to 'Open'.</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
@@ -13085,7 +13097,7 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 395 - Inspection Work Order record is updated, and only if Inspection Employee compares to 'None'.</t>
+          <t>Runs when a 395 - Inspection Work Order record is updated, and only if InspectionEmployee ?.</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -13131,7 +13143,7 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 300 - Account Management record is updated, and only if Dispatch to Installation Contractor is 'True' and Primary Contractor is at least '06b924d0-99ae-a554-1893-3a12bf2fd6a8'.</t>
+          <t>Runs when a 300 - Account Management record is updated, and only if Dispatch to Installation Contractor is 'True' and Primary Contractor compares to '06b924d0-99ae-a554-1893-3a12bf2fd6a8'.</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -13177,7 +13189,7 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 300 - Account Management record is updated, and only if DP Invoice Received Date compares to '2025-05-14T07:20:00-07:00' or Down Payment Invoice Number compares to 'None' and Request Down Payment is 'True' and Submit Final Invoice is 'None'.</t>
+          <t>Runs when a 300 - Account Management record is updated, and only if DP Invoice Received Date compares to '2025-05-14T07:20:00-07:00' or DPInvoiceNumber ? and Request Down Payment is 'True' and InvoiceInstallation ==.</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -13453,7 +13465,7 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 300 - Account Management record is updated, and only if Final Invoice Amount compares to 'None' or Final Invoice Number compares to 'None' and Submit Final Invoice is 'True'.</t>
+          <t>Runs when a 300 - Account Management record is updated, and only if InstallationInvoiceAmount ? or InstallationInvoiceNumber ? and Submit Final Invoice is 'True'.</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -13499,7 +13511,7 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 395 - Inspection Work Order record is updated, and only if Inspection Notes compares to 'None'.</t>
+          <t>Runs when a 395 - Inspection Work Order record is updated, and only if InspectionNotes ?.</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -13545,7 +13557,7 @@
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 395 - Inspection Work Order record is updated, and only if Inspection Notes compares to 'None'.</t>
+          <t>Runs when a 395 - Inspection Work Order record is updated, and only if InspectionNotes ?.</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -13591,7 +13603,7 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 300 - Account Management record is updated, and only if Invoice Enrollment is 'True' and Enrollment Invoice Amount compares to 'None'.</t>
+          <t>Runs when a 300 - Account Management record is updated, and only if Invoice Enrollment is 'True' and EnrollmentInvoiceAmount ?.</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -13637,7 +13649,7 @@
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 300 - Account Management record is updated, and only if Request Down Payment is 'True' and DP Invoice Received Date compares to '2025-05-20T09:36:00-07:00' and Submit Final Invoice is 'None'.</t>
+          <t>Runs when a 300 - Account Management record is updated, and only if Request Down Payment is 'True' and DP Invoice Received Date compares to '2025-05-20T09:36:00-07:00' and InvoiceInstallation ==.</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -13729,7 +13741,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Management Review Status (Enrollment) is 'Rejected' and Invoice Status Note (Enrollment) compares to 'None'.</t>
+          <t>Runs when a Invoice record is updated, and only if Management Review Status (Enrollment) is 'Rejected' and EnrollmentNoteSummary ?.</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -13821,7 +13833,7 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 395 - Inspection Work Order record is updated, and only if Inspection Note compares to 'None'.</t>
+          <t>Runs when a 395 - Inspection Work Order record is updated, and only if MostRecentNote ?.</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -13867,7 +13879,7 @@
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 395 - Inspection Work Order record is updated, and only if Inspection Status compares to 'None'.</t>
+          <t>Runs when a 395 - Inspection Work Order record is updated, and only if ComputedInspectionStatus ?.</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
@@ -14005,7 +14017,7 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Review Status - Coordinator (Final) is 'Pending Corrections' or Review Status - PM (Final) is 'Pending Corrections' or Review Status - Management (Final) is 'Pending Corrections' and Invoice Status Note (Final) compares to 'None' and Invoice Status (Final) is 'Pending Corrections'.</t>
+          <t>Runs when a Invoice record is updated, and only if Review Status - Coordinator (Final) is 'Pending Corrections' or Review Status - PM (Final) is 'Pending Corrections' or Review Status - Management (Final) is 'Pending Corrections' and InvoiceNoteSummary ? and Invoice Status (Final) is 'Pending Corrections'.</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -14051,7 +14063,7 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Coordinator Review Status (Enrollment) is 'Corrections Required' or Management Review Status (Enrollment) is 'Corrections Required' or PM Review Status (Enrollment) is 'Corrections Required' and Invoice Status Note (Enrollment) compares to 'None'.</t>
+          <t>Runs when a Invoice record is updated, and only if Coordinator Review Status (Enrollment) is 'Corrections Required' or Management Review Status (Enrollment) is 'Corrections Required' or PM Review Status (Enrollment) is 'Corrections Required' and EnrollmentNoteSummary ?.</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -14235,7 +14247,7 @@
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 310 - Enrollment Intake record is updated, and only if Enrollment Status compares to 'None' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 310 - Enrollment Intake record is updated, and only if EnrollmentSubmissionStatus ? and ReviewedBy_c ?.</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -14281,7 +14293,7 @@
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 315 - SoCal WHP Assessment record is updated, and only if Assessment Status compares to 'None' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 315 - SoCal WHP Assessment record is updated, and only if AssessementStatus_c ? and ReviewerName_c ?.</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -14327,7 +14339,7 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 325 - SoCal Installation record is updated, and only if Installation Status compares to 'None' and Reviewer Name compares to 'None'.</t>
+          <t>Runs when a 325 - SoCal Installation record is updated, and only if InstallationStatus_c ? and ReviewerName_c ?.</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -14373,7 +14385,7 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Runs when a Invoice record is updated, and only if Invoice Status (Final) compares to 'None' and Processor Name (Final) compares to 'None' and Invoice Status (Final) is at least 'Pending Review'.</t>
+          <t>Runs when a Invoice record is updated, and only if InvoiceStatusSummary ? and ProcessorName_Final_c ? and Invoice Status (Final) compares to 'Pending Review'.</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -14419,7 +14431,7 @@
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Runs when a 300 - Account Management record is updated, and only if Invoice Assessment is 'True' and Assessment Invoice Amount compares to 'None'.</t>
+          <t>Runs when a 300 - Account Management record is updated, and only if Invoice Assessment is 'True' and AssessmentInvoiceAmount ?.</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
@@ -15617,7 +15629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -15704,41 +15716,61 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>liwp, nve-qar, sce-be, sdge-whp</t>
+          <t>liwp, nve-qar, sce-be</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>liwp/INSPECTION_NEW_WORK_ORDER, liwp/INSPECTION_WORK_ORDER_ASSIGNED, liwp/INVOICE_INVOICE_SUBMITTED_BY, nve-qar/895_DISPATCH_TO_USER, sce-be/200_CUSTOMER_INTEREST, sce-be/INVOICE_INVOICE_SUBMITTED_BY_2, sce-be/210_UPDATE_RECORDS, sce-be/255_UPDATE_RECORDS, sdge-whp/ACCOUNT_REFRESH_ACCOUNT</t>
+          <t>liwp/INSPECTION_NEW_WORK_ORDER, liwp/INSPECTION_WORK_ORDER_ASSIGNED, liwp/INVOICE_INVOICE_SUBMITTED_BY, nve-qar/895_DISPATCH_TO_USER, sce-be/200_CUSTOMER_INTEREST, sce-be/INVOICE_INVOICE_SUBMITTED_BY_2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
+          <t>Create -&gt; 210 - Enrollment &amp; Assessment Form</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>sce-be</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>sce-be/210_UPDATE_RECORDS, sce-be/200_CREATE_ENROLLMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
           <t>Update -&gt; Account Management (400)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>sdge-whp</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>sdge-whp/410_UPDATE_ACCOUNT, sdge-whp/415_UPDATE_ACCOUNT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D7"/>
+  <autoFilter ref="A3:D8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
